--- a/backend/data_pengiriman.xlsx
+++ b/backend/data_pengiriman.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07f44b35b9511d77/Tài liệu/logistik_1/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C59007B-6350-464F-B96C-96FB22A19106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{8C59007B-6350-464F-B96C-96FB22A19106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7195F7A3-8F0C-41AB-9F6C-A704F9BFB250}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{EEE27158-FAF6-44F6-A9FE-C335B6F7A039}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EEE27158-FAF6-44F6-A9FE-C335B6F7A039}"/>
   </bookViews>
   <sheets>
     <sheet name="pawenang" sheetId="1" r:id="rId1"/>
